--- a/data/raw/marcas.xlsx
+++ b/data/raw/marcas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drp_d\Documents\diegorp\mkt_intelligence\mkt_intelligence_dw\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6DE26E-AB76-4F8C-998F-0FC49F7A1FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F28539F-6AA1-4BDE-998B-0BFC03D5C0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7945F23-4C21-44DA-83A9-32B236E4DAC6}"/>
   </bookViews>
@@ -41,90 +41,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
   <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>mainstream</t>
   </si>
   <si>
     <t>premium</t>
   </si>
   <si>
-    <t>Rubi</t>
-  </si>
-  <si>
-    <t>Esmera</t>
-  </si>
-  <si>
-    <t>Safira</t>
-  </si>
-  <si>
-    <t>Ava_Brasil</t>
-  </si>
-  <si>
-    <t>Brada</t>
-  </si>
-  <si>
-    <t>Crypto</t>
-  </si>
-  <si>
-    <t>Polo</t>
-  </si>
-  <si>
-    <t>Nova</t>
-  </si>
-  <si>
-    <t>Origem</t>
-  </si>
-  <si>
-    <t>Ava_Premium</t>
-  </si>
-  <si>
-    <t>Devaneios</t>
-  </si>
-  <si>
-    <t>Ava_Malte</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>Star</t>
-  </si>
-  <si>
-    <t>Pina</t>
-  </si>
-  <si>
-    <t>Budapeste</t>
-  </si>
-  <si>
-    <t>Pedra</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Paternalista</t>
-  </si>
-  <si>
-    <t>Duo_Brada</t>
-  </si>
-  <si>
-    <t>Amiga</t>
-  </si>
-  <si>
-    <t>Istelotto</t>
-  </si>
-  <si>
-    <t>Kombat</t>
-  </si>
-  <si>
-    <t>Daki</t>
-  </si>
-  <si>
-    <t>Boah</t>
-  </si>
-  <si>
     <t>codigo_marca</t>
   </si>
   <si>
@@ -135,16 +57,101 @@
   </si>
   <si>
     <t>nome_fabricante</t>
+  </si>
+  <si>
+    <t>Brava Malt</t>
+  </si>
+  <si>
+    <t>Pedra Clara</t>
+  </si>
+  <si>
+    <t>Norte Real</t>
+  </si>
+  <si>
+    <t>Vento Sul</t>
+  </si>
+  <si>
+    <t>Trilha Pilsen</t>
+  </si>
+  <si>
+    <t>Ferro Velho</t>
+  </si>
+  <si>
+    <t>Lenda Negra</t>
+  </si>
+  <si>
+    <t>Boa Safra</t>
+  </si>
+  <si>
+    <t>Porto Alto</t>
+  </si>
+  <si>
+    <t>Serra Alta</t>
+  </si>
+  <si>
+    <t>Estacao 7</t>
+  </si>
+  <si>
+    <t>Mare Brava</t>
+  </si>
+  <si>
+    <t>Maltera</t>
+  </si>
+  <si>
+    <t>Luprex</t>
+  </si>
+  <si>
+    <t>Brevum</t>
+  </si>
+  <si>
+    <t>low_price</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>Golden Vil</t>
+  </si>
+  <si>
+    <t>Monte Lups</t>
+  </si>
+  <si>
+    <t>Ribeira Las</t>
+  </si>
+  <si>
+    <t>Raiz e Malte</t>
+  </si>
+  <si>
+    <t>Casa Lupulo</t>
+  </si>
+  <si>
+    <t>Good Sun</t>
+  </si>
+  <si>
+    <t>Master Lin</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Vila Cerva</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,8 +177,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,324 +523,324 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5000</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5050</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5100</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5150</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5200</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
+      <c r="C6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5250</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5300</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5350</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5400</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5450</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>5500</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5550</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5600</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5650</v>
       </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>5700</v>
       </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>5</v>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>5750</v>
       </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5800</v>
       </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>5850</v>
       </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>3</v>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>5900</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>5</v>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>5950</v>
       </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6000</v>
       </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>5</v>
+      <c r="B22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>6050</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>3</v>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
